--- a/3-能力管理/运行记录类文件/030204-2025年1-12月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年1-12月运维服务能力改进计划及跟踪.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="22185" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t xml:space="preserve">
 2025年运维服务能力改进计划及跟踪</t>
@@ -86,13 +86,13 @@
     <t>运维部</t>
   </si>
   <si>
-    <t>2025年10月20日前完成</t>
+    <t>2025年12月20日前完成</t>
   </si>
   <si>
     <t>已完成</t>
   </si>
   <si>
-    <t>2025.10.16</t>
+    <t>2025.12.16</t>
   </si>
   <si>
     <t>郑云</t>
@@ -128,7 +128,6 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>由服</t>
@@ -138,7 +137,6 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>务台负责人进行集体培训来提高服务台人员的用语规</t>
@@ -148,7 +146,6 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>范性，从而提高用户的整体满</t>
@@ -158,59 +155,38 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
-        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>意度。</t>
     </r>
   </si>
   <si>
-    <t>2025年11月20日前完成</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025年12月20日前完成</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.11.16</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.12.16</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <t>2025年12月31日前完成</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -218,7 +194,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -227,7 +202,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -236,7 +210,6 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -244,7 +217,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -253,7 +225,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -262,7 +233,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -271,7 +241,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -280,7 +249,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -289,7 +257,6 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -297,7 +264,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -306,7 +272,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -315,7 +280,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -324,7 +288,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -332,7 +295,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -341,7 +303,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -349,7 +310,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -357,7 +317,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -365,7 +324,6 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -373,31 +331,19 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -457,19 +403,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59996337778862885"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599963377788629"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,19 +427,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59996337778862885"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599963377788629"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,19 +451,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59996337778862885"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599963377788629"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,19 +475,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59996337778862885"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599963377788629"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -553,19 +499,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59996337778862885"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599963377788629"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,19 +523,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59996337778862885"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599963377788629"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -600,6 +546,84 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -631,7 +655,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.49995422223578601"/>
+        <color theme="4" tint="0.499954222235786"/>
       </bottom>
       <diagonal/>
     </border>
@@ -700,233 +724,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="54" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="53" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
-    <cellStyle name="20% - 强调文字颜色 1" xfId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="35"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="39"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="43"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="47"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="51"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="32"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="36"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="40"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="44"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="48"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="52"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="33"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="37"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="41"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="45"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="49"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="53"/>
-    <cellStyle name="Comma" xfId="4"/>
-    <cellStyle name="Comma [0]" xfId="5"/>
-    <cellStyle name="Currency" xfId="2"/>
-    <cellStyle name="Currency [0]" xfId="3"/>
-    <cellStyle name="Normal" xfId="54"/>
-    <cellStyle name="Percent" xfId="1"/>
-    <cellStyle name="百分比" xfId="8"/>
-    <cellStyle name="标题" xfId="15"/>
-    <cellStyle name="标题 1" xfId="17"/>
-    <cellStyle name="标题 2" xfId="18"/>
-    <cellStyle name="标题 3" xfId="19"/>
-    <cellStyle name="标题 4" xfId="20"/>
-    <cellStyle name="差" xfId="28"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="11"/>
-    <cellStyle name="好" xfId="27"/>
-    <cellStyle name="汇总" xfId="26"/>
-    <cellStyle name="货币" xfId="7"/>
-    <cellStyle name="货币[0]" xfId="10"/>
-    <cellStyle name="计算" xfId="23"/>
-    <cellStyle name="检查单元格" xfId="24"/>
-    <cellStyle name="解释性文本" xfId="16"/>
-    <cellStyle name="警告文本" xfId="14"/>
-    <cellStyle name="链接单元格" xfId="25"/>
-    <cellStyle name="千位分隔" xfId="6"/>
-    <cellStyle name="千位分隔[0]" xfId="9"/>
-    <cellStyle name="强调文字颜色 1" xfId="30"/>
-    <cellStyle name="强调文字颜色 2" xfId="34"/>
-    <cellStyle name="强调文字颜色 3" xfId="38"/>
-    <cellStyle name="强调文字颜色 4" xfId="42"/>
-    <cellStyle name="强调文字颜色 5" xfId="46"/>
-    <cellStyle name="强调文字颜色 6" xfId="50"/>
-    <cellStyle name="适中" xfId="29"/>
-    <cellStyle name="输出" xfId="22"/>
-    <cellStyle name="输入" xfId="21"/>
-    <cellStyle name="已访问的超链接" xfId="12"/>
-    <cellStyle name="注释" xfId="13"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Comma" xfId="49"/>
+    <cellStyle name="Comma [0]" xfId="50"/>
+    <cellStyle name="Currency" xfId="51"/>
+    <cellStyle name="Currency [0]" xfId="52"/>
+    <cellStyle name="Normal" xfId="53"/>
+    <cellStyle name="Percent" xfId="54"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1217,180 +1159,180 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
+    <col min="5" max="5" width="27.5555555555556" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="41.25" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" ht="26.25" customHeight="1">
+    <row r="2" ht="26.25" customHeight="1" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="6" t="s">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="7"/>
     </row>
-    <row r="3" spans="1:10" ht="26.25" customHeight="1">
+    <row r="3" ht="26.25" customHeight="1" spans="1:10">
       <c r="A3" s="3"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="129.94999999999999" customHeight="1">
-      <c r="A4" s="9">
+    <row r="4" ht="129.95" customHeight="1" spans="1:10">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="36">
-      <c r="A5" s="9">
+    <row r="5" ht="48" spans="1:10">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="62.4" spans="1:10">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="57">
-      <c r="A6" s="9">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1402,8 +1344,8 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="87" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="87" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/3-能力管理/运行记录类文件/030204-2025年1-12月运维服务能力改进计划及跟踪.xlsx
+++ b/3-能力管理/运行记录类文件/030204-2025年1-12月运维服务能力改进计划及跟踪.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowHeight="18180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
-    <t xml:space="preserve">
-2025年运维服务能力改进计划及跟踪</t>
+    <t>2025年运维服务能力改进计划及跟踪</t>
   </si>
   <si>
     <t>序号</t>
@@ -1166,19 +1165,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
-    <col min="4" max="4" width="17.8796296296296" customWidth="1"/>
-    <col min="5" max="5" width="27.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="17.8833333333333" customWidth="1"/>
+    <col min="5" max="5" width="27.5583333333333" customWidth="1"/>
     <col min="6" max="6" width="12.75" customWidth="1"/>
     <col min="7" max="7" width="11.25" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="12.3796296296296" customWidth="1"/>
+    <col min="9" max="9" width="12.3833333333333" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="41.25" customHeight="1" spans="1:10">
+    <row r="1" ht="21" customHeight="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1239,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="129.95" customHeight="1" spans="1:10">
+    <row r="4" ht="78" customHeight="1" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -1272,7 +1271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" ht="48" spans="1:10">
+    <row r="5" ht="41" customHeight="1" spans="1:10">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -1304,7 +1303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="62.4" spans="1:10">
+    <row r="6" ht="57" spans="1:10">
       <c r="A6" s="3">
         <v>3</v>
       </c>
